--- a/GATEWAY/tarasoft/tarasoft_/45801/2.0/report-checklist.xlsx
+++ b/GATEWAY/tarasoft/tarasoft_/45801/2.0/report-checklist.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="33720" yWindow="980" windowWidth="19420" windowHeight="11020" tabRatio="490" activeTab="2"/>
@@ -1384,6 +1384,9 @@
     <t>subject_application_id:45801</t>
   </si>
   <si>
+    <t>subject_application_vendor:tarasoft_</t>
+  </si>
+  <si>
     <t>subject_application_version:2.0</t>
   </si>
   <si>
@@ -1393,6 +1396,18 @@
     <t>VALIDAZIONE_CDA2_RSA_CT25_OK</t>
   </si>
   <si>
+    <t>c6754f133aa8a4965f44a4c104032329</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.910128636be06d441b232825151baa3731af884810e3dfd1cb6f9f5893fe1f42.f04de7fa7f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>9cbc7fc4a304d9ca41bd516b0058d76a</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.910128636be06d441b232825151baa3731af884810e3dfd1cb6f9f5893fe1f42.cbcf1aca31^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
     <t>ALLINEAMENTO DB CON SISS LOMBARDIA</t>
   </si>
   <si>
@@ -1456,9 +1471,21 @@
     <t>VALIDAZIONE_CDA2_RAD_CT25_OK</t>
   </si>
   <si>
+    <t>9a56d9d564da1168781347d26c091dc5</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.c22af8628943b0adb82544199d15d420c6cd8e41f8aafdecbf0c09ead259b9a3.1c373e6879^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
     <t>VALIDAZIONE_CDA2_RAD_CT26_OK</t>
   </si>
   <si>
+    <t>3383d2f8fa6a422d67eaad9314253f10</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.c22af8628943b0adb82544199d15d420c6cd8e41f8aafdecbf0c09ead259b9a3.c7e3643747^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
     <t>d5752852c2256166990db7f2300e0802</t>
   </si>
   <si>
@@ -1660,6 +1687,12 @@
     <t>2.16.840.1.113883.2.9.2.30.4.4.910128636be06d441b232825151baa3731af884810e3dfd1cb6f9f5893fe1f42.89636a2fe9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
+    <t>2025-12-27T15:14:21Z</t>
+  </si>
+  <si>
+    <t>2025-12-27T16:09:06Z</t>
+  </si>
+  <si>
     <t>2025-12-28T04:56:38Z</t>
   </si>
   <si>
@@ -1705,6 +1738,12 @@
     <t>2026-01-08T10:05:31Z</t>
   </si>
   <si>
+    <t>2025-12-26T16:01:45Z</t>
+  </si>
+  <si>
+    <t>2025-12-26T17:54:42Z</t>
+  </si>
+  <si>
     <t>2025-12-27T06:28:33Z</t>
   </si>
   <si>
@@ -1853,45 +1892,6 @@
   </si>
   <si>
     <t>7d76fdbbed91fbda87e5806a6a3bb822</t>
-  </si>
-  <si>
-    <t>subject_application_vendor:tarasoft_</t>
-  </si>
-  <si>
-    <t>2026-02-12T16:08:50Z</t>
-  </si>
-  <si>
-    <t>3164163aa44a694114387fac3c06e26e</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.c22af8628943b0adb82544199d15d420c6cd8e41f8aafdecbf0c09ead259b9a3.a0d69ef0dc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-02-12T16:16:31Z</t>
-  </si>
-  <si>
-    <t>8468b76c0edae9eec42e20729922ba57</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.c22af8628943b0adb82544199d15d420c6cd8e41f8aafdecbf0c09ead259b9a3.b833fa52a5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-02-12T18:49:06Z</t>
-  </si>
-  <si>
-    <t>06a055ae46f66b7eb3d9808cc7a9486f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.910128636be06d441b232825151baa3731af884810e3dfd1cb6f9f5893fe1f42.12173fbf30^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-02-12T18:52:20Z</t>
-  </si>
-  <si>
-    <t>4ceb4e8753c849869086958006b0f6be</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.910128636be06d441b232825151baa3731af884810e3dfd1cb6f9f5893fe1f42.e788d7a794^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4114,7 +4114,7 @@
       <c r="A4" s="72"/>
       <c r="B4" s="73"/>
       <c r="C4" s="76" t="s">
-        <v>505</v>
+        <v>348</v>
       </c>
       <c r="D4" s="68"/>
       <c r="E4" s="4"/>
@@ -4141,7 +4141,7 @@
       <c r="A5" s="74"/>
       <c r="B5" s="75"/>
       <c r="C5" s="76" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D5" s="68"/>
       <c r="F5" s="6"/>
@@ -9318,7 +9318,7 @@
         <v>38</v>
       </c>
       <c r="D145" s="33" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E145" s="41" t="s">
         <v>43</v>
@@ -9327,13 +9327,13 @@
         <v>46055</v>
       </c>
       <c r="G145" s="64" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="H145" s="64" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="I145" s="40" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="J145" s="36" t="s">
         <v>60</v>
@@ -9357,7 +9357,7 @@
         <v>191</v>
       </c>
       <c r="S145" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T145" s="36" t="s">
         <v>189</v>
@@ -9379,7 +9379,7 @@
         <v>38</v>
       </c>
       <c r="D146" s="33" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="E146" s="41" t="s">
         <v>53</v>
@@ -9388,13 +9388,13 @@
         <v>46055</v>
       </c>
       <c r="G146" s="64" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="H146" s="64" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="I146" s="61" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="J146" s="36" t="s">
         <v>60</v>
@@ -9418,7 +9418,7 @@
         <v>191</v>
       </c>
       <c r="S146" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T146" s="36" t="s">
         <v>189</v>
@@ -9440,7 +9440,7 @@
         <v>38</v>
       </c>
       <c r="D147" s="33" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E147" s="41" t="s">
         <v>333</v>
@@ -9449,7 +9449,7 @@
         <v>46030</v>
       </c>
       <c r="G147" s="35" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="H147" s="35"/>
       <c r="I147" s="40"/>
@@ -9475,7 +9475,7 @@
         <v>191</v>
       </c>
       <c r="S147" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T147" s="36" t="s">
         <v>189</v>
@@ -9497,22 +9497,22 @@
         <v>38</v>
       </c>
       <c r="D148" s="33" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E148" s="41" t="s">
         <v>332</v>
       </c>
       <c r="F148" s="35">
-        <v>46065</v>
-      </c>
-      <c r="G148" s="64" t="s">
-        <v>506</v>
-      </c>
-      <c r="H148" s="64" t="s">
-        <v>507</v>
-      </c>
-      <c r="I148" s="61" t="s">
-        <v>508</v>
+        <v>46018</v>
+      </c>
+      <c r="G148" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="H148" s="35" t="s">
+        <v>377</v>
+      </c>
+      <c r="I148" s="40" t="s">
+        <v>378</v>
       </c>
       <c r="J148" s="36" t="s">
         <v>60</v>
@@ -9546,22 +9546,22 @@
         <v>38</v>
       </c>
       <c r="D149" s="33" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="E149" s="41" t="s">
         <v>332</v>
       </c>
       <c r="F149" s="35">
-        <v>46065</v>
-      </c>
-      <c r="G149" s="64" t="s">
-        <v>509</v>
-      </c>
-      <c r="H149" s="64" t="s">
-        <v>510</v>
-      </c>
-      <c r="I149" s="61" t="s">
-        <v>511</v>
+        <v>46018</v>
+      </c>
+      <c r="G149" s="35" t="s">
+        <v>450</v>
+      </c>
+      <c r="H149" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="I149" s="40" t="s">
+        <v>381</v>
       </c>
       <c r="J149" s="36" t="s">
         <v>60</v>
@@ -9595,7 +9595,7 @@
         <v>38</v>
       </c>
       <c r="D150" s="33" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E150" s="41" t="s">
         <v>332</v>
@@ -9604,13 +9604,13 @@
         <v>46019</v>
       </c>
       <c r="G150" s="35" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="H150" s="35" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="I150" s="40" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="J150" s="36" t="s">
         <v>60</v>
@@ -9634,14 +9634,14 @@
         <v>191</v>
       </c>
       <c r="S150" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T150" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U150" s="37"/>
       <c r="V150" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W150" s="36" t="s">
         <v>44</v>
@@ -9658,7 +9658,7 @@
         <v>38</v>
       </c>
       <c r="D151" s="33" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="E151" s="41" t="s">
         <v>332</v>
@@ -9667,13 +9667,13 @@
         <v>46049</v>
       </c>
       <c r="G151" s="35" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="H151" s="35" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="I151" s="40" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="J151" s="36" t="s">
         <v>60</v>
@@ -9697,14 +9697,14 @@
         <v>191</v>
       </c>
       <c r="S151" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T151" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U151" s="37"/>
       <c r="V151" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W151" s="36" t="s">
         <v>44</v>
@@ -9721,7 +9721,7 @@
         <v>38</v>
       </c>
       <c r="D152" s="33" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="E152" s="41" t="s">
         <v>332</v>
@@ -9730,13 +9730,13 @@
         <v>46049</v>
       </c>
       <c r="G152" s="35" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="H152" s="35" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="I152" s="40" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="J152" s="36" t="s">
         <v>60</v>
@@ -9760,14 +9760,14 @@
         <v>191</v>
       </c>
       <c r="S152" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T152" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U152" s="37"/>
       <c r="V152" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W152" s="36" t="s">
         <v>44</v>
@@ -9784,7 +9784,7 @@
         <v>38</v>
       </c>
       <c r="D153" s="33" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="E153" s="41" t="s">
         <v>332</v>
@@ -9793,13 +9793,13 @@
         <v>46049</v>
       </c>
       <c r="G153" s="35" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="H153" s="35" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="I153" s="40" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="J153" s="36" t="s">
         <v>60</v>
@@ -9823,14 +9823,14 @@
         <v>191</v>
       </c>
       <c r="S153" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T153" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U153" s="37"/>
       <c r="V153" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W153" s="36" t="s">
         <v>44</v>
@@ -9847,7 +9847,7 @@
         <v>38</v>
       </c>
       <c r="D154" s="33" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="E154" s="41" t="s">
         <v>332</v>
@@ -9856,13 +9856,13 @@
         <v>46049</v>
       </c>
       <c r="G154" s="35" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="H154" s="35" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="I154" s="40" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="J154" s="36" t="s">
         <v>60</v>
@@ -9886,14 +9886,14 @@
         <v>191</v>
       </c>
       <c r="S154" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T154" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U154" s="37"/>
       <c r="V154" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W154" s="36" t="s">
         <v>44</v>
@@ -9910,7 +9910,7 @@
         <v>38</v>
       </c>
       <c r="D155" s="33" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="E155" s="41" t="s">
         <v>332</v>
@@ -9919,13 +9919,13 @@
         <v>46019</v>
       </c>
       <c r="G155" s="35" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="H155" s="35" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="I155" s="40" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="J155" s="36" t="s">
         <v>60</v>
@@ -9949,14 +9949,14 @@
         <v>191</v>
       </c>
       <c r="S155" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T155" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U155" s="37"/>
       <c r="V155" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W155" s="36" t="s">
         <v>44</v>
@@ -9973,7 +9973,7 @@
         <v>38</v>
       </c>
       <c r="D156" s="33" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="E156" s="41" t="s">
         <v>332</v>
@@ -9982,13 +9982,13 @@
         <v>46019</v>
       </c>
       <c r="G156" s="35" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="H156" s="35" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="I156" s="40" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="J156" s="36" t="s">
         <v>60</v>
@@ -10012,14 +10012,14 @@
         <v>191</v>
       </c>
       <c r="S156" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T156" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U156" s="37"/>
       <c r="V156" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W156" s="36" t="s">
         <v>44</v>
@@ -10036,7 +10036,7 @@
         <v>38</v>
       </c>
       <c r="D157" s="33" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E157" s="41" t="s">
         <v>332</v>
@@ -10045,13 +10045,13 @@
         <v>46019</v>
       </c>
       <c r="G157" s="35" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="H157" s="35" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="I157" s="40" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="J157" s="36" t="s">
         <v>60</v>
@@ -10075,14 +10075,14 @@
         <v>191</v>
       </c>
       <c r="S157" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T157" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U157" s="37"/>
       <c r="V157" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W157" s="36" t="s">
         <v>44</v>
@@ -10099,7 +10099,7 @@
         <v>38</v>
       </c>
       <c r="D158" s="33" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="E158" s="41" t="s">
         <v>332</v>
@@ -10108,13 +10108,13 @@
         <v>46019</v>
       </c>
       <c r="G158" s="35" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="H158" s="35" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="I158" s="40" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="J158" s="36" t="s">
         <v>60</v>
@@ -10138,14 +10138,14 @@
         <v>191</v>
       </c>
       <c r="S158" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T158" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U158" s="37"/>
       <c r="V158" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W158" s="36" t="s">
         <v>44</v>
@@ -10162,7 +10162,7 @@
         <v>38</v>
       </c>
       <c r="D159" s="33" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E159" s="41" t="s">
         <v>332</v>
@@ -10171,13 +10171,13 @@
         <v>46019</v>
       </c>
       <c r="G159" s="35" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="H159" s="35" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="I159" s="40" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="J159" s="36" t="s">
         <v>60</v>
@@ -10201,14 +10201,14 @@
         <v>191</v>
       </c>
       <c r="S159" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T159" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U159" s="37"/>
       <c r="V159" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W159" s="36" t="s">
         <v>44</v>
@@ -10225,7 +10225,7 @@
         <v>38</v>
       </c>
       <c r="D160" s="33" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="E160" s="41" t="s">
         <v>332</v>
@@ -10234,13 +10234,13 @@
         <v>46019</v>
       </c>
       <c r="G160" s="35" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="H160" s="35" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="I160" s="40" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="J160" s="36" t="s">
         <v>60</v>
@@ -10264,14 +10264,14 @@
         <v>191</v>
       </c>
       <c r="S160" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T160" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U160" s="37"/>
       <c r="V160" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W160" s="36" t="s">
         <v>44</v>
@@ -10288,7 +10288,7 @@
         <v>38</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E161" s="41" t="s">
         <v>332</v>
@@ -10297,13 +10297,13 @@
         <v>46019</v>
       </c>
       <c r="G161" s="35" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="H161" s="35" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="I161" s="40" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J161" s="36" t="s">
         <v>60</v>
@@ -10327,14 +10327,14 @@
         <v>191</v>
       </c>
       <c r="S161" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T161" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U161" s="37"/>
       <c r="V161" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W161" s="36" t="s">
         <v>44</v>
@@ -10351,7 +10351,7 @@
         <v>38</v>
       </c>
       <c r="D162" s="33" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="E162" s="41" t="s">
         <v>332</v>
@@ -10360,13 +10360,13 @@
         <v>46019</v>
       </c>
       <c r="G162" s="35" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H162" s="35" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="I162" s="40" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="J162" s="36" t="s">
         <v>60</v>
@@ -10390,14 +10390,14 @@
         <v>191</v>
       </c>
       <c r="S162" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T162" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U162" s="37"/>
       <c r="V162" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W162" s="36" t="s">
         <v>44</v>
@@ -10414,7 +10414,7 @@
         <v>38</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="E163" s="41" t="s">
         <v>332</v>
@@ -10423,13 +10423,13 @@
         <v>46019</v>
       </c>
       <c r="G163" s="35" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="H163" s="35" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="I163" s="40" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="J163" s="36" t="s">
         <v>60</v>
@@ -10453,14 +10453,14 @@
         <v>191</v>
       </c>
       <c r="S163" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T163" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U163" s="37"/>
       <c r="V163" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W163" s="36" t="s">
         <v>44</v>
@@ -10477,7 +10477,7 @@
         <v>38</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="E164" s="41" t="s">
         <v>332</v>
@@ -10486,13 +10486,13 @@
         <v>46019</v>
       </c>
       <c r="G164" s="35" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="H164" s="35" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="I164" s="40" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="J164" s="36" t="s">
         <v>60</v>
@@ -10516,14 +10516,14 @@
         <v>191</v>
       </c>
       <c r="S164" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T164" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U164" s="37"/>
       <c r="V164" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W164" s="36" t="s">
         <v>44</v>
@@ -10540,7 +10540,7 @@
         <v>38</v>
       </c>
       <c r="D165" s="33" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="E165" s="41" t="s">
         <v>332</v>
@@ -10549,13 +10549,13 @@
         <v>46049</v>
       </c>
       <c r="G165" s="35" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="H165" s="35" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="I165" s="40" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="J165" s="36" t="s">
         <v>60</v>
@@ -10579,14 +10579,14 @@
         <v>191</v>
       </c>
       <c r="S165" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T165" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U165" s="37"/>
       <c r="V165" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W165" s="36" t="s">
         <v>44</v>
@@ -10603,7 +10603,7 @@
         <v>38</v>
       </c>
       <c r="D166" s="33" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E166" s="41" t="s">
         <v>332</v>
@@ -10612,13 +10612,13 @@
         <v>46019</v>
       </c>
       <c r="G166" s="35" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="H166" s="35" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="I166" s="40" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="J166" s="36" t="s">
         <v>60</v>
@@ -10642,14 +10642,14 @@
         <v>191</v>
       </c>
       <c r="S166" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T166" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U166" s="37"/>
       <c r="V166" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W166" s="36" t="s">
         <v>44</v>
@@ -10666,7 +10666,7 @@
         <v>38</v>
       </c>
       <c r="D167" s="33" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="E167" s="41" t="s">
         <v>332</v>
@@ -10675,13 +10675,13 @@
         <v>46019</v>
       </c>
       <c r="G167" s="35" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="H167" s="35" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="I167" s="40" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="J167" s="36" t="s">
         <v>60</v>
@@ -10705,14 +10705,14 @@
         <v>191</v>
       </c>
       <c r="S167" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T167" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U167" s="37"/>
       <c r="V167" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W167" s="36" t="s">
         <v>44</v>
@@ -10729,7 +10729,7 @@
         <v>48</v>
       </c>
       <c r="D168" s="33" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="E168" s="41" t="s">
         <v>43</v>
@@ -10738,13 +10738,13 @@
         <v>46055</v>
       </c>
       <c r="G168" s="64" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="H168" s="64" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="I168" s="61" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="J168" s="36" t="s">
         <v>60</v>
@@ -10768,7 +10768,7 @@
         <v>191</v>
       </c>
       <c r="S168" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T168" s="36" t="s">
         <v>189</v>
@@ -10790,7 +10790,7 @@
         <v>48</v>
       </c>
       <c r="D169" s="33" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E169" s="41" t="s">
         <v>53</v>
@@ -10799,13 +10799,13 @@
         <v>46055</v>
       </c>
       <c r="G169" s="64" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="H169" s="64" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="I169" s="61" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="J169" s="36" t="s">
         <v>60</v>
@@ -10829,7 +10829,7 @@
         <v>191</v>
       </c>
       <c r="S169" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T169" s="36" t="s">
         <v>189</v>
@@ -10851,7 +10851,7 @@
         <v>48</v>
       </c>
       <c r="D170" s="33" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E170" s="41" t="s">
         <v>333</v>
@@ -10860,7 +10860,7 @@
         <v>46030</v>
       </c>
       <c r="G170" s="35" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="H170" s="35"/>
       <c r="I170" s="40"/>
@@ -10886,7 +10886,7 @@
         <v>191</v>
       </c>
       <c r="S170" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T170" s="36" t="s">
         <v>189</v>
@@ -10908,22 +10908,22 @@
         <v>48</v>
       </c>
       <c r="D171" s="33" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E171" s="41" t="s">
         <v>332</v>
       </c>
       <c r="F171" s="35">
-        <v>46065</v>
-      </c>
-      <c r="G171" s="64" t="s">
-        <v>512</v>
-      </c>
-      <c r="H171" s="64" t="s">
-        <v>513</v>
-      </c>
-      <c r="I171" s="61" t="s">
-        <v>514</v>
+        <v>46017</v>
+      </c>
+      <c r="G171" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="H171" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="I171" s="40" t="s">
+        <v>353</v>
       </c>
       <c r="J171" s="36" t="s">
         <v>60</v>
@@ -11068,22 +11068,22 @@
         <v>48</v>
       </c>
       <c r="D175" s="33" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E175" s="41" t="s">
         <v>332</v>
       </c>
       <c r="F175" s="35">
-        <v>46065</v>
-      </c>
-      <c r="G175" s="64" t="s">
-        <v>515</v>
-      </c>
-      <c r="H175" s="64" t="s">
-        <v>516</v>
-      </c>
-      <c r="I175" s="61" t="s">
-        <v>517</v>
+        <v>46017</v>
+      </c>
+      <c r="G175" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="H175" s="35" t="s">
+        <v>354</v>
+      </c>
+      <c r="I175" s="40" t="s">
+        <v>355</v>
       </c>
       <c r="J175" s="36" t="s">
         <v>60</v>
@@ -11117,7 +11117,7 @@
         <v>48</v>
       </c>
       <c r="D176" s="33" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E176" s="41" t="s">
         <v>332</v>
@@ -11126,13 +11126,13 @@
         <v>46018</v>
       </c>
       <c r="G176" s="35" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="H176" s="35" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="I176" s="40" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="J176" s="36" t="s">
         <v>60</v>
@@ -11156,14 +11156,14 @@
         <v>191</v>
       </c>
       <c r="S176" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T176" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U176" s="37"/>
       <c r="V176" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W176" s="36" t="s">
         <v>44</v>
@@ -11180,7 +11180,7 @@
         <v>48</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E177" s="41" t="s">
         <v>332</v>
@@ -11189,13 +11189,13 @@
         <v>46049</v>
       </c>
       <c r="G177" s="35" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="H177" s="35" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="I177" s="40" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="J177" s="36" t="s">
         <v>60</v>
@@ -11219,14 +11219,14 @@
         <v>191</v>
       </c>
       <c r="S177" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T177" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U177" s="37"/>
       <c r="V177" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W177" s="36" t="s">
         <v>44</v>
@@ -11243,7 +11243,7 @@
         <v>48</v>
       </c>
       <c r="D178" s="33" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E178" s="41" t="s">
         <v>332</v>
@@ -11252,13 +11252,13 @@
         <v>46049</v>
       </c>
       <c r="G178" s="35" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="H178" s="35" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="I178" s="40" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="J178" s="36" t="s">
         <v>60</v>
@@ -11282,14 +11282,14 @@
         <v>191</v>
       </c>
       <c r="S178" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T178" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U178" s="37"/>
       <c r="V178" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W178" s="36" t="s">
         <v>44</v>
@@ -11315,13 +11315,13 @@
         <v>46049</v>
       </c>
       <c r="G179" s="35" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="H179" s="35" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="I179" s="40" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="J179" s="36" t="s">
         <v>60</v>
@@ -11345,14 +11345,14 @@
         <v>191</v>
       </c>
       <c r="S179" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T179" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U179" s="37"/>
       <c r="V179" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W179" s="36" t="s">
         <v>44</v>
@@ -11378,13 +11378,13 @@
         <v>46018</v>
       </c>
       <c r="G180" s="35" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="H180" s="35" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I180" s="40" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="J180" s="36" t="s">
         <v>60</v>
@@ -11408,14 +11408,14 @@
         <v>191</v>
       </c>
       <c r="S180" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T180" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U180" s="37"/>
       <c r="V180" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W180" s="36" t="s">
         <v>44</v>
@@ -11441,13 +11441,13 @@
         <v>46018</v>
       </c>
       <c r="G181" s="35" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="H181" s="35" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I181" s="40" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="J181" s="36" t="s">
         <v>60</v>
@@ -11471,14 +11471,14 @@
         <v>191</v>
       </c>
       <c r="S181" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T181" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U181" s="37"/>
       <c r="V181" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W181" s="36" t="s">
         <v>44</v>
@@ -11504,13 +11504,13 @@
         <v>46018</v>
       </c>
       <c r="G182" s="35" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="H182" s="35" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I182" s="40" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="J182" s="36" t="s">
         <v>60</v>
@@ -11534,14 +11534,14 @@
         <v>191</v>
       </c>
       <c r="S182" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T182" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U182" s="37"/>
       <c r="V182" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W182" s="36" t="s">
         <v>44</v>
@@ -11567,13 +11567,13 @@
         <v>46049</v>
       </c>
       <c r="G183" s="35" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="H183" s="35" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="I183" s="40" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="J183" s="36" t="s">
         <v>60</v>
@@ -11597,14 +11597,14 @@
         <v>191</v>
       </c>
       <c r="S183" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T183" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U183" s="37"/>
       <c r="V183" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W183" s="36" t="s">
         <v>44</v>
@@ -11630,13 +11630,13 @@
         <v>46018</v>
       </c>
       <c r="G184" s="35" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="H184" s="35" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="I184" s="40" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="J184" s="36" t="s">
         <v>60</v>
@@ -11660,14 +11660,14 @@
         <v>191</v>
       </c>
       <c r="S184" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T184" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U184" s="37"/>
       <c r="V184" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W184" s="36" t="s">
         <v>44</v>
@@ -11693,13 +11693,13 @@
         <v>46018</v>
       </c>
       <c r="G185" s="35" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="H185" s="35" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="I185" s="40" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="J185" s="36" t="s">
         <v>60</v>
@@ -11723,14 +11723,14 @@
         <v>191</v>
       </c>
       <c r="S185" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T185" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U185" s="37"/>
       <c r="V185" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W185" s="36" t="s">
         <v>44</v>
@@ -11756,13 +11756,13 @@
         <v>46018</v>
       </c>
       <c r="G186" s="35" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="H186" s="35" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="I186" s="40" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="J186" s="36" t="s">
         <v>60</v>
@@ -11786,14 +11786,14 @@
         <v>191</v>
       </c>
       <c r="S186" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T186" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U186" s="37"/>
       <c r="V186" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W186" s="36" t="s">
         <v>44</v>
@@ -11819,13 +11819,13 @@
         <v>46018</v>
       </c>
       <c r="G187" s="35" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="H187" s="35" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I187" s="40" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="J187" s="36" t="s">
         <v>60</v>
@@ -11849,14 +11849,14 @@
         <v>191</v>
       </c>
       <c r="S187" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T187" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U187" s="37"/>
       <c r="V187" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W187" s="36" t="s">
         <v>44</v>
@@ -11882,13 +11882,13 @@
         <v>46018</v>
       </c>
       <c r="G188" s="35" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H188" s="35" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="I188" s="40" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="J188" s="36" t="s">
         <v>60</v>
@@ -11912,14 +11912,14 @@
         <v>191</v>
       </c>
       <c r="S188" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T188" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U188" s="37"/>
       <c r="V188" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W188" s="36" t="s">
         <v>44</v>
@@ -11945,13 +11945,13 @@
         <v>46018</v>
       </c>
       <c r="G189" s="35" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="H189" s="35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I189" s="40" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="J189" s="36" t="s">
         <v>60</v>
@@ -11975,14 +11975,14 @@
         <v>191</v>
       </c>
       <c r="S189" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T189" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U189" s="37"/>
       <c r="V189" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W189" s="36" t="s">
         <v>44</v>
@@ -12008,13 +12008,13 @@
         <v>46018</v>
       </c>
       <c r="G190" s="35" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="H190" s="35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I190" s="40" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J190" s="36" t="s">
         <v>60</v>
@@ -12038,14 +12038,14 @@
         <v>191</v>
       </c>
       <c r="S190" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T190" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U190" s="37"/>
       <c r="V190" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W190" s="36" t="s">
         <v>44</v>
@@ -12071,13 +12071,13 @@
         <v>46018</v>
       </c>
       <c r="G191" s="35" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="H191" s="35" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I191" s="40" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="J191" s="36" t="s">
         <v>60</v>
@@ -12101,14 +12101,14 @@
         <v>191</v>
       </c>
       <c r="S191" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T191" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U191" s="37"/>
       <c r="V191" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W191" s="36" t="s">
         <v>44</v>
@@ -12125,7 +12125,7 @@
         <v>48</v>
       </c>
       <c r="D192" s="33" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E192" s="41" t="s">
         <v>332</v>
@@ -12134,13 +12134,13 @@
         <v>46018</v>
       </c>
       <c r="G192" s="35" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="H192" s="35" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="I192" s="40" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="J192" s="36" t="s">
         <v>60</v>
@@ -12164,14 +12164,14 @@
         <v>191</v>
       </c>
       <c r="S192" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T192" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U192" s="37"/>
       <c r="V192" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W192" s="36" t="s">
         <v>44</v>
@@ -12188,7 +12188,7 @@
         <v>48</v>
       </c>
       <c r="D193" s="33" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E193" s="41" t="s">
         <v>332</v>
@@ -12197,13 +12197,13 @@
         <v>46018</v>
       </c>
       <c r="G193" s="35" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="H193" s="35" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I193" s="40" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="J193" s="36" t="s">
         <v>60</v>
@@ -12227,14 +12227,14 @@
         <v>191</v>
       </c>
       <c r="S193" s="36" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="T193" s="36" t="s">
         <v>189</v>
       </c>
       <c r="U193" s="37"/>
       <c r="V193" s="38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="W193" s="36" t="s">
         <v>44</v>
@@ -15840,7 +15840,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
@@ -15960,7 +15960,7 @@
         <v>471.47199999999998</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -15974,7 +15974,7 @@
         <v>448.44900000000001</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
